--- a/气象/表格文件/单一站或位置/单站各冬低温阈值天数和冬均最低气温.xlsx
+++ b/气象/表格文件/单一站或位置/单站各冬低温阈值天数和冬均最低气温.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\单一站或位置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AD32A4-6B1E-4C1A-B828-675439D39463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E6AC47-4B86-4207-BF57-A904000A3C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{D308DEC9-CED1-4015-BAB2-E937FD661EDE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="230">
   <si>
     <t>冬季</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -987,203 +987,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>共 16 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 14 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 49 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 34 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 12 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 9 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 20 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 38 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 56 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 45 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 28 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 69 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 25 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 17 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 13 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 51 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 21 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 15 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 3 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 8 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 5 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 4 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 2 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 6 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 37 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 1 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 7 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 11 天低温达到 -50°C</t>
-  </si>
-  <si>
-    <t>共 10 天低温达到 -50°C</t>
-  </si>
-  <si>
     <t>无 -40℃</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">期间 共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">922天 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">低温达到 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-40℃</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">冬均最低 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-43.8℃</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1961-1990</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">冬均最低 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-44..8℃</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1261,6 +1065,183 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">冬均最低 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-43.8℃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">共 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">922天 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">低温达到 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-40℃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>低温</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="24"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-40℃</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="24"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>天数</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>共 16 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 14 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 49 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 34 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 12 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 9 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 20 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 38 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 56 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 45 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 28 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 69 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 25 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 17 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 13 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 51 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 21 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 15 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 3 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 8 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 5 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 4 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 2 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 6 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 37 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 1 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 7 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 11 天低温达到 -40°C</t>
+  </si>
+  <si>
+    <t>共 10 天低温达到 -40°C</t>
+  </si>
 </sst>
 </file>
 
@@ -1270,7 +1251,7 @@
     <numFmt numFmtId="176" formatCode="0.0\℃"/>
     <numFmt numFmtId="177" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1455,6 +1436,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1614,7 +1604,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1732,6 +1722,12 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1745,7 +1741,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="12" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1774,6 +1770,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="12" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1782,18 +1781,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2138,36 +2125,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
     </row>
     <row r="2" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="42"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="44"/>
       <c r="D2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="45"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="51" t="s">
+      <c r="F2" s="47"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="I2" s="52"/>
+      <c r="I2" s="54"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="24" t="s">
@@ -4191,21 +4178,21 @@
       <c r="O79" s="3"/>
     </row>
     <row r="80" spans="1:15" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="46" t="s">
+      <c r="A80" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="B80" s="47"/>
-      <c r="C80" s="48"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="50"/>
       <c r="D80" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="E80" s="43" t="s">
+      <c r="E80" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="F80" s="53"/>
-      <c r="G80" s="44"/>
-      <c r="H80" s="54"/>
-      <c r="I80" s="55"/>
+      <c r="F80" s="56"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="57"/>
+      <c r="I80" s="58"/>
     </row>
     <row r="81" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F81" s="21"/>
@@ -4293,12 +4280,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
       <c r="E1"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -4308,10 +4295,10 @@
       <c r="B2" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="42"/>
+      <c r="D2" s="44"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
@@ -5318,10 +5305,10 @@
       <c r="B70" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="43" t="s">
+      <c r="C70" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="44"/>
+      <c r="D70" s="46"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D68">
@@ -5372,12 +5359,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="A1" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
       <c r="E1"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -5385,19 +5372,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="42"/>
+      <c r="D2" s="44"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>193</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>15</v>
@@ -5412,7 +5399,7 @@
         <v>194</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>15</v>
@@ -5427,12 +5414,12 @@
         <v>192</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>-49.6</v>
       </c>
       <c r="E5" s="3"/>
@@ -5442,7 +5429,7 @@
         <v>123</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>10</v>
@@ -5457,7 +5444,7 @@
         <v>124</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>10</v>
@@ -5472,7 +5459,7 @@
         <v>125</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>10</v>
@@ -5486,8 +5473,8 @@
       <c r="A9" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="58" t="s">
-        <v>202</v>
+      <c r="B9" s="40" t="s">
+        <v>207</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>10</v>
@@ -5502,7 +5489,7 @@
         <v>127</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>10</v>
@@ -5516,8 +5503,8 @@
       <c r="A11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="57" t="s">
-        <v>204</v>
+      <c r="B11" s="39" t="s">
+        <v>209</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>10</v>
@@ -5532,7 +5519,7 @@
         <v>129</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>10</v>
@@ -5546,8 +5533,8 @@
       <c r="A13" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="58" t="s">
-        <v>206</v>
+      <c r="B13" s="40" t="s">
+        <v>211</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>10</v>
@@ -5561,8 +5548,8 @@
       <c r="A14" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="56" t="s">
-        <v>207</v>
+      <c r="B14" s="13" t="s">
+        <v>212</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>10</v>
@@ -5577,7 +5564,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>10</v>
@@ -5591,8 +5578,8 @@
       <c r="A16" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="58" t="s">
-        <v>208</v>
+      <c r="B16" s="40" t="s">
+        <v>213</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>10</v>
@@ -5607,7 +5594,7 @@
         <v>134</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>10</v>
@@ -5622,7 +5609,7 @@
         <v>135</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>10</v>
@@ -5637,7 +5624,7 @@
         <v>136</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>10</v>
@@ -5652,7 +5639,7 @@
         <v>137</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>10</v>
@@ -5667,7 +5654,7 @@
         <v>138</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>10</v>
@@ -5681,8 +5668,8 @@
       <c r="A22" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="57" t="s">
-        <v>211</v>
+      <c r="B22" s="39" t="s">
+        <v>216</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>10</v>
@@ -5696,8 +5683,8 @@
       <c r="A23" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="58" t="s">
-        <v>212</v>
+      <c r="B23" s="40" t="s">
+        <v>217</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>10</v>
@@ -5712,7 +5699,7 @@
         <v>141</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>10</v>
@@ -5727,7 +5714,7 @@
         <v>142</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>10</v>
@@ -5742,7 +5729,7 @@
         <v>143</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>10</v>
@@ -5757,7 +5744,7 @@
         <v>144</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>10</v>
@@ -5772,7 +5759,7 @@
         <v>145</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>10</v>
@@ -5787,7 +5774,7 @@
         <v>146</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>10</v>
@@ -5802,7 +5789,7 @@
         <v>147</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>10</v>
@@ -5817,7 +5804,7 @@
         <v>148</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>10</v>
@@ -5831,8 +5818,8 @@
       <c r="A32" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="58" t="s">
-        <v>202</v>
+      <c r="B32" s="40" t="s">
+        <v>207</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>10</v>
@@ -5847,7 +5834,7 @@
         <v>150</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>10</v>
@@ -5862,7 +5849,7 @@
         <v>151</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>10</v>
@@ -5877,7 +5864,7 @@
         <v>152</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>10</v>
@@ -5892,12 +5879,12 @@
         <v>153</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="16">
         <v>-39.200000000000003</v>
       </c>
       <c r="E36" s="3"/>
@@ -5907,7 +5894,7 @@
         <v>154</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>10</v>
@@ -5922,7 +5909,7 @@
         <v>155</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>10</v>
@@ -5937,7 +5924,7 @@
         <v>156</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>10</v>
@@ -5952,7 +5939,7 @@
         <v>157</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>10</v>
@@ -5967,7 +5954,7 @@
         <v>158</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>10</v>
@@ -5982,7 +5969,7 @@
         <v>159</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>10</v>
@@ -5997,7 +5984,7 @@
         <v>160</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>10</v>
@@ -6012,7 +5999,7 @@
         <v>161</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>10</v>
@@ -6027,7 +6014,7 @@
         <v>162</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>10</v>
@@ -6042,7 +6029,7 @@
         <v>163</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>10</v>
@@ -6057,7 +6044,7 @@
         <v>164</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>10</v>
@@ -6072,7 +6059,7 @@
         <v>165</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>10</v>
@@ -6087,7 +6074,7 @@
         <v>166</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>10</v>
@@ -6102,7 +6089,7 @@
         <v>167</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>10</v>
@@ -6117,7 +6104,7 @@
         <v>168</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>10</v>
@@ -6132,12 +6119,12 @@
         <v>169</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="16">
         <v>-39.200000000000003</v>
       </c>
       <c r="E52" s="3"/>
@@ -6147,7 +6134,7 @@
         <v>170</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>10</v>
@@ -6162,7 +6149,7 @@
         <v>171</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>10</v>
@@ -6177,7 +6164,7 @@
         <v>172</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>10</v>
@@ -6192,7 +6179,7 @@
         <v>173</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>10</v>
@@ -6207,7 +6194,7 @@
         <v>174</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>10</v>
@@ -6221,8 +6208,8 @@
       <c r="A58" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B58" s="58" t="s">
-        <v>212</v>
+      <c r="B58" s="40" t="s">
+        <v>217</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>10</v>
@@ -6237,7 +6224,7 @@
         <v>176</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>10</v>
@@ -6247,17 +6234,17 @@
       </c>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:5" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="18" t="s">
         <v>195</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="C60" s="59" t="s">
-        <v>227</v>
-      </c>
-      <c r="D60" s="44"/>
+        <v>199</v>
+      </c>
+      <c r="C60" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="D60" s="46"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D59">

--- a/气象/表格文件/单一站或位置/单站各冬低温阈值天数和冬均最低气温.xlsx
+++ b/气象/表格文件/单一站或位置/单站各冬低温阈值天数和冬均最低气温.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\单一站或位置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E6AC47-4B86-4207-BF57-A904000A3C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E5EDCD-3263-442B-9382-95E3FE0D70FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{D308DEC9-CED1-4015-BAB2-E937FD661EDE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{D308DEC9-CED1-4015-BAB2-E937FD661EDE}"/>
   </bookViews>
   <sheets>
     <sheet name="中卡拉尔" sheetId="3" r:id="rId1"/>
     <sheet name="乌斯季卡连加" sheetId="1" r:id="rId2"/>
-    <sheet name="根河" sheetId="5" r:id="rId3"/>
+    <sheet name="巴彦特斯" sheetId="6" r:id="rId3"/>
+    <sheet name="根河" sheetId="5" r:id="rId4"/>
+    <sheet name="北极村" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="251">
   <si>
     <t>冬季</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1242,6 +1244,223 @@
   <si>
     <t>共 10 天低温达到 -40°C</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="32"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">巴彦特斯 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="32"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-40℃ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="32"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>气温天数</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="24"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>巴彦特斯</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:    49.70°N    96.36°E    1420m        蒙古·扎布汗·巴彦特斯苏木    人口约 2300</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">冬均最低 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-46.9℃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">共 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">389天 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">低温达到 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-40℃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">共 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 冬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>共 1 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 35 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 16 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 32 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 37 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 12 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 19 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 34 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 10 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 27 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 31 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 14 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 13 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 17 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 21 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 9 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 15 天低温达到 -40℃</t>
+  </si>
 </sst>
 </file>
 
@@ -1251,7 +1470,7 @@
     <numFmt numFmtId="176" formatCode="0.0\℃"/>
     <numFmt numFmtId="177" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1445,6 +1664,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1604,7 +1832,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1728,6 +1956,9 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1782,6 +2013,9 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1791,12 +2025,12 @@
   <colors>
     <mruColors>
       <color rgb="FF3A0CA3"/>
+      <color rgb="FF3F37C9"/>
+      <color rgb="FF7209B7"/>
       <color rgb="FF4361EE"/>
       <color rgb="FF4895EF"/>
       <color rgb="FF4CC9F0"/>
-      <color rgb="FF3F37C9"/>
       <color rgb="FF560BAD"/>
-      <color rgb="FF7209B7"/>
       <color rgb="FFB5179E"/>
       <color rgb="FFF72585"/>
       <color rgb="FF480CA8"/>
@@ -2125,36 +2359,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="44"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="45"/>
       <c r="D2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="53" t="s">
+      <c r="F2" s="48"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="I2" s="54"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="24" t="s">
@@ -4178,21 +4412,21 @@
       <c r="O79" s="3"/>
     </row>
     <row r="80" spans="1:15" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="48" t="s">
+      <c r="A80" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="B80" s="49"/>
-      <c r="C80" s="50"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="51"/>
       <c r="D80" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="E80" s="55" t="s">
+      <c r="E80" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="F80" s="56"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="57"/>
-      <c r="I80" s="58"/>
+      <c r="F80" s="57"/>
+      <c r="G80" s="47"/>
+      <c r="H80" s="58"/>
+      <c r="I80" s="59"/>
     </row>
     <row r="81" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F81" s="21"/>
@@ -4280,12 +4514,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
       <c r="E1"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -4295,10 +4529,10 @@
       <c r="B2" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="44"/>
+      <c r="D2" s="45"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
@@ -5305,10 +5539,10 @@
       <c r="B70" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="55" t="s">
+      <c r="C70" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="46"/>
+      <c r="D70" s="47"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D68">
@@ -5347,6 +5581,387 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D620BB74-1CB0-4429-AD86-9E8DB0D3CFDC}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56.59765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.59765625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="24.59765625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1"/>
+    </row>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="45"/>
+    </row>
+    <row r="3" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="16">
+        <v>-40.799999999999997</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="17">
+        <v>-48.8</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="17">
+        <v>-47</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="17">
+        <v>-49</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="17">
+        <v>-50.1</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="17">
+        <v>-48</v>
+      </c>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="17">
+        <v>-48</v>
+      </c>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="17">
+        <v>-44.7</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="17">
+        <v>-41</v>
+      </c>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="17">
+        <v>-48.7</v>
+      </c>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="17">
+        <v>-44.7</v>
+      </c>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="16">
+        <v>-51.8</v>
+      </c>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="17">
+        <v>-45.3</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="17">
+        <v>-48.4</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="17">
+        <v>-48</v>
+      </c>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="17">
+        <v>-44.3</v>
+      </c>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="17">
+        <v>-50</v>
+      </c>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="17">
+        <v>-46.7</v>
+      </c>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="17">
+        <v>-42.3</v>
+      </c>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="17">
+        <v>-51.1</v>
+      </c>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="D23" s="47"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D22">
+    <sortCondition ref="A3:A22"/>
+  </sortState>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C23:D23"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D3:D22">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF72585"/>
+        <color rgb="FF7209B7"/>
+        <color rgb="FF3A0CA3"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF72585"/>
+        <color rgb="FF7209B7"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C975CB41-FCB2-48DA-BDED-0B1D083382E3}">
   <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
@@ -5359,12 +5974,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
       <c r="E1"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -5374,10 +5989,10 @@
       <c r="B2" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="44"/>
+      <c r="D2" s="45"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
@@ -6241,10 +6856,10 @@
       <c r="B60" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="C60" s="45" t="s">
+      <c r="C60" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="D60" s="46"/>
+      <c r="D60" s="47"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D59">
@@ -6280,4 +6895,937 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCEE6757-B0B8-42FF-89E9-C5F50BDD2B9D}">
+  <dimension ref="A1:E60"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56.59765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.59765625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="24.59765625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1"/>
+    </row>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="45"/>
+    </row>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="17">
+        <v>-44.7</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="17">
+        <v>-46</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="16">
+        <v>-49.6</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="17">
+        <v>-48.5</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="17">
+        <v>-43.4</v>
+      </c>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="17">
+        <v>-43.7</v>
+      </c>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="17">
+        <v>-43.6</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="17">
+        <v>-46.6</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="17">
+        <v>-49.2</v>
+      </c>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="17">
+        <v>-46.5</v>
+      </c>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="17">
+        <v>-46.7</v>
+      </c>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="17">
+        <v>-49.1</v>
+      </c>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="17">
+        <v>-48.1</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="17">
+        <v>-47.6</v>
+      </c>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="17">
+        <v>-42.1</v>
+      </c>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="17">
+        <v>-44.4</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="17">
+        <v>-43.9</v>
+      </c>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="17">
+        <v>-43.6</v>
+      </c>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="17">
+        <v>-44.1</v>
+      </c>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="17">
+        <v>-45.9</v>
+      </c>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="17">
+        <v>-42.8</v>
+      </c>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="17">
+        <v>-45.5</v>
+      </c>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="17">
+        <v>-45.5</v>
+      </c>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="17">
+        <v>-42.5</v>
+      </c>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="17">
+        <v>-43.7</v>
+      </c>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="17">
+        <v>-43.3</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="17">
+        <v>-44.7</v>
+      </c>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="17">
+        <v>-44.5</v>
+      </c>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="17">
+        <v>-41.5</v>
+      </c>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="17">
+        <v>-45.3</v>
+      </c>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="17">
+        <v>-43.7</v>
+      </c>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="17">
+        <v>-39.799999999999997</v>
+      </c>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="17">
+        <v>-45</v>
+      </c>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="16">
+        <v>-39.200000000000003</v>
+      </c>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="17">
+        <v>-41.1</v>
+      </c>
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="17">
+        <v>-41</v>
+      </c>
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="17">
+        <v>-42.3</v>
+      </c>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="17">
+        <v>-39.4</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="17">
+        <v>-41.4</v>
+      </c>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="17">
+        <v>-44.3</v>
+      </c>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="17">
+        <v>-43.6</v>
+      </c>
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="17">
+        <v>-40.700000000000003</v>
+      </c>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="17">
+        <v>-43.4</v>
+      </c>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="17">
+        <v>-47.5</v>
+      </c>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="17">
+        <v>-40.299999999999997</v>
+      </c>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="17">
+        <v>-42</v>
+      </c>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="17">
+        <v>-41</v>
+      </c>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="17">
+        <v>-41.5</v>
+      </c>
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="17">
+        <v>-42.6</v>
+      </c>
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="16">
+        <v>-39.200000000000003</v>
+      </c>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="17">
+        <v>-42</v>
+      </c>
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="17">
+        <v>-40.4</v>
+      </c>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="17">
+        <v>-44.7</v>
+      </c>
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="17">
+        <v>-43.8</v>
+      </c>
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="17">
+        <v>-44.2</v>
+      </c>
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="17">
+        <v>-43.2</v>
+      </c>
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="17">
+        <v>-42.1</v>
+      </c>
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="1:5" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C60" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="D60" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C60:D60"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D3:D59">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF72585"/>
+        <color rgb="FF7209B7"/>
+        <color rgb="FF3A0CA3"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF72585"/>
+        <color rgb="FF7209B7"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/气象/表格文件/单一站或位置/单站各冬低温阈值天数和冬均最低气温.xlsx
+++ b/气象/表格文件/单一站或位置/单站各冬低温阈值天数和冬均最低气温.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\单一站或位置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E5EDCD-3263-442B-9382-95E3FE0D70FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1310703A-3257-45FA-A9D4-9F4753DA127E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{D308DEC9-CED1-4015-BAB2-E937FD661EDE}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="270">
   <si>
     <t>冬季</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -943,10 +943,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>低温-50℃天数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1959~1960冬</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1128,36 +1124,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>低温</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="24"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-40℃</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="24"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>天数</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>共 16 天低温达到 -40°C</t>
   </si>
   <si>
@@ -1461,6 +1427,265 @@
   <si>
     <t>共 15 天低温达到 -40℃</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">冬均最低 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-45.5℃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">共 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">739天 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">低温达到 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-40℃</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">共 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>39</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 冬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>共 3 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 5 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 6 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 11 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 18 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 20 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 24 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 26 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 28 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 36 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 38 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 48 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <t>共 63 天低温达到 -40℃</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1957</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>~1958冬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1995~</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1996</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>冬</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="32"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">漠河『北极村』 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="32"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-40℃ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="32"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>气温天数</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">低温 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="24"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-40℃ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="24"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>天数</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低温 -50℃ 天数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1470,7 +1695,7 @@
     <numFmt numFmtId="176" formatCode="0.0\℃"/>
     <numFmt numFmtId="177" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1673,6 +1898,24 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFF00"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1832,7 +2075,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1959,7 +2202,13 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2013,8 +2262,8 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2024,15 +2273,15 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF3A0CA3"/>
+      <color rgb="FFF72585"/>
+      <color rgb="FFB5179E"/>
+      <color rgb="FF560BAD"/>
       <color rgb="FF3F37C9"/>
-      <color rgb="FF7209B7"/>
       <color rgb="FF4361EE"/>
       <color rgb="FF4895EF"/>
       <color rgb="FF4CC9F0"/>
-      <color rgb="FF560BAD"/>
-      <color rgb="FFB5179E"/>
-      <color rgb="FFF72585"/>
+      <color rgb="FF3A0CA3"/>
+      <color rgb="FF7209B7"/>
       <color rgb="FF480CA8"/>
     </mruColors>
   </colors>
@@ -2359,36 +2608,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
     </row>
     <row r="2" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="45"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="47"/>
       <c r="D2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="48"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="54" t="s">
+      <c r="F2" s="50"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="I2" s="55"/>
+      <c r="I2" s="57"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="24" t="s">
@@ -4412,21 +4661,21 @@
       <c r="O79" s="3"/>
     </row>
     <row r="80" spans="1:15" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="49" t="s">
+      <c r="A80" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="B80" s="50"/>
-      <c r="C80" s="51"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="53"/>
       <c r="D80" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="E80" s="56" t="s">
+      <c r="E80" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="F80" s="57"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="58"/>
-      <c r="I80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="60"/>
+      <c r="I80" s="61"/>
     </row>
     <row r="81" spans="6:6" x14ac:dyDescent="0.4">
       <c r="F81" s="21"/>
@@ -4514,12 +4763,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="62" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
       <c r="E1"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -4527,12 +4776,12 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="45"/>
+      <c r="D2" s="47"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
@@ -5539,10 +5788,10 @@
       <c r="B70" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="56" t="s">
+      <c r="C70" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="47"/>
+      <c r="D70" s="49"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D68">
@@ -5593,12 +5842,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="42" t="s">
-        <v>230</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="A1" s="62" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
       <c r="E1"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -5606,19 +5855,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="C2" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="45"/>
+      <c r="D2" s="47"/>
     </row>
     <row r="3" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="60" t="s">
-        <v>234</v>
+      <c r="B3" s="42" t="s">
+        <v>232</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>15</v>
@@ -5633,7 +5882,7 @@
         <v>170</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>10</v>
@@ -5648,7 +5897,7 @@
         <v>171</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>10</v>
@@ -5663,7 +5912,7 @@
         <v>172</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>10</v>
@@ -5678,7 +5927,7 @@
         <v>173</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>10</v>
@@ -5693,7 +5942,7 @@
         <v>174</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>10</v>
@@ -5708,7 +5957,7 @@
         <v>175</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>10</v>
@@ -5723,7 +5972,7 @@
         <v>176</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>10</v>
@@ -5737,8 +5986,8 @@
       <c r="A11" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B11" s="60" t="s">
-        <v>234</v>
+      <c r="B11" s="42" t="s">
+        <v>232</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>10</v>
@@ -5753,7 +6002,7 @@
         <v>178</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>10</v>
@@ -5768,7 +6017,7 @@
         <v>179</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>10</v>
@@ -5783,7 +6032,7 @@
         <v>180</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>10</v>
@@ -5798,7 +6047,7 @@
         <v>181</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>10</v>
@@ -5813,7 +6062,7 @@
         <v>182</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>10</v>
@@ -5828,7 +6077,7 @@
         <v>183</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>10</v>
@@ -5843,7 +6092,7 @@
         <v>184</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>10</v>
@@ -5858,7 +6107,7 @@
         <v>185</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>10</v>
@@ -5873,7 +6122,7 @@
         <v>186</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>10</v>
@@ -5888,7 +6137,7 @@
         <v>187</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>10</v>
@@ -5903,7 +6152,7 @@
         <v>188</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>10</v>
@@ -5915,15 +6164,15 @@
     </row>
     <row r="23" spans="1:5" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="18" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="D23" s="47"/>
+        <v>230</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>229</v>
+      </c>
+      <c r="D23" s="49"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D22">
@@ -5974,12 +6223,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="A1" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
       <c r="E1"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -5987,19 +6236,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="C2" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="45"/>
+      <c r="D2" s="47"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>15</v>
@@ -6011,10 +6260,10 @@
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>15</v>
@@ -6026,10 +6275,10 @@
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>15</v>
@@ -6044,7 +6293,7 @@
         <v>123</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>10</v>
@@ -6059,7 +6308,7 @@
         <v>124</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>10</v>
@@ -6074,7 +6323,7 @@
         <v>125</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>10</v>
@@ -6089,7 +6338,7 @@
         <v>126</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>10</v>
@@ -6104,7 +6353,7 @@
         <v>127</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>10</v>
@@ -6119,7 +6368,7 @@
         <v>128</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>10</v>
@@ -6134,7 +6383,7 @@
         <v>129</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>10</v>
@@ -6149,7 +6398,7 @@
         <v>130</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>10</v>
@@ -6164,7 +6413,7 @@
         <v>131</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>10</v>
@@ -6179,7 +6428,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>10</v>
@@ -6194,7 +6443,7 @@
         <v>133</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>10</v>
@@ -6209,7 +6458,7 @@
         <v>134</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>10</v>
@@ -6224,7 +6473,7 @@
         <v>135</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>10</v>
@@ -6239,7 +6488,7 @@
         <v>136</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>10</v>
@@ -6254,7 +6503,7 @@
         <v>137</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>10</v>
@@ -6269,7 +6518,7 @@
         <v>138</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>10</v>
@@ -6284,7 +6533,7 @@
         <v>139</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>10</v>
@@ -6299,7 +6548,7 @@
         <v>140</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>10</v>
@@ -6314,7 +6563,7 @@
         <v>141</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>10</v>
@@ -6329,7 +6578,7 @@
         <v>142</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>10</v>
@@ -6344,7 +6593,7 @@
         <v>143</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>10</v>
@@ -6359,7 +6608,7 @@
         <v>144</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>10</v>
@@ -6374,7 +6623,7 @@
         <v>145</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>10</v>
@@ -6389,7 +6638,7 @@
         <v>146</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>10</v>
@@ -6404,7 +6653,7 @@
         <v>147</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>10</v>
@@ -6419,7 +6668,7 @@
         <v>148</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>10</v>
@@ -6434,7 +6683,7 @@
         <v>149</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>10</v>
@@ -6449,7 +6698,7 @@
         <v>150</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>10</v>
@@ -6464,7 +6713,7 @@
         <v>151</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>10</v>
@@ -6479,7 +6728,7 @@
         <v>152</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>10</v>
@@ -6494,7 +6743,7 @@
         <v>153</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>10</v>
@@ -6509,7 +6758,7 @@
         <v>154</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>10</v>
@@ -6524,7 +6773,7 @@
         <v>155</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>10</v>
@@ -6539,7 +6788,7 @@
         <v>156</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>10</v>
@@ -6554,7 +6803,7 @@
         <v>157</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>10</v>
@@ -6569,7 +6818,7 @@
         <v>158</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>10</v>
@@ -6584,7 +6833,7 @@
         <v>159</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>10</v>
@@ -6599,7 +6848,7 @@
         <v>160</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>10</v>
@@ -6614,7 +6863,7 @@
         <v>161</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>10</v>
@@ -6629,7 +6878,7 @@
         <v>162</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>10</v>
@@ -6644,7 +6893,7 @@
         <v>163</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>10</v>
@@ -6659,7 +6908,7 @@
         <v>164</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>10</v>
@@ -6674,7 +6923,7 @@
         <v>165</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>10</v>
@@ -6689,7 +6938,7 @@
         <v>166</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>10</v>
@@ -6704,7 +6953,7 @@
         <v>167</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>10</v>
@@ -6719,7 +6968,7 @@
         <v>168</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>10</v>
@@ -6734,7 +6983,7 @@
         <v>169</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>10</v>
@@ -6749,7 +6998,7 @@
         <v>170</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>10</v>
@@ -6764,7 +7013,7 @@
         <v>171</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>10</v>
@@ -6779,7 +7028,7 @@
         <v>172</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>10</v>
@@ -6794,7 +7043,7 @@
         <v>173</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>10</v>
@@ -6809,7 +7058,7 @@
         <v>174</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>10</v>
@@ -6824,7 +7073,7 @@
         <v>175</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>10</v>
@@ -6839,7 +7088,7 @@
         <v>176</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>10</v>
@@ -6851,15 +7100,15 @@
     </row>
     <row r="60" spans="1:5" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C60" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="D60" s="47"/>
+      <c r="C60" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="D60" s="49"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D59">
@@ -6899,7 +7148,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCEE6757-B0B8-42FF-89E9-C5F50BDD2B9D}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.59765625" style="1" customWidth="1"/>
@@ -6910,12 +7159,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="A1" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
       <c r="E1"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -6923,55 +7172,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="C2" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="45"/>
+      <c r="D2" s="47"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>193</v>
+        <v>265</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="17">
-        <v>-44.7</v>
+        <v>-46.1</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="17">
-        <v>-46</v>
+        <v>-46.2</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>203</v>
+        <v>191</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>235</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="16">
-        <v>-49.6</v>
+      <c r="D5" s="17">
+        <v>-46.2</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -6979,14 +7228,14 @@
       <c r="A6" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>204</v>
+      <c r="B6" s="25" t="s">
+        <v>235</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="17">
-        <v>-48.5</v>
+        <v>-49.1</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -6995,13 +7244,13 @@
         <v>124</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="17">
-        <v>-43.4</v>
+        <v>-44.2</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -7010,13 +7259,13 @@
         <v>125</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>206</v>
+        <v>254</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="17">
-        <v>-43.7</v>
+        <v>-44.7</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -7024,14 +7273,14 @@
       <c r="A9" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="40" t="s">
-        <v>207</v>
+      <c r="B9" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="17">
-        <v>-43.6</v>
+        <v>-40.4</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -7039,14 +7288,14 @@
       <c r="A10" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>208</v>
+      <c r="B10" s="25" t="s">
+        <v>261</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="17">
-        <v>-46.6</v>
+        <v>-47.5</v>
       </c>
       <c r="E10" s="3"/>
     </row>
@@ -7055,13 +7304,13 @@
         <v>128</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="17">
-        <v>-49.2</v>
+        <v>-47.2</v>
       </c>
       <c r="E11" s="3"/>
     </row>
@@ -7069,14 +7318,14 @@
       <c r="A12" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>210</v>
+      <c r="B12" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="17">
-        <v>-46.5</v>
+        <v>-41.4</v>
       </c>
       <c r="E12" s="3"/>
     </row>
@@ -7084,14 +7333,14 @@
       <c r="A13" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="40" t="s">
-        <v>211</v>
+      <c r="B13" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="17">
-        <v>-46.7</v>
+        <v>-43.2</v>
       </c>
       <c r="E13" s="3"/>
     </row>
@@ -7100,13 +7349,13 @@
         <v>131</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>212</v>
+        <v>264</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="17">
-        <v>-49.1</v>
+      <c r="D14" s="16">
+        <v>-52.3</v>
       </c>
       <c r="E14" s="3"/>
     </row>
@@ -7114,14 +7363,14 @@
       <c r="A15" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>203</v>
+      <c r="B15" s="40" t="s">
+        <v>258</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="17">
-        <v>-48.1</v>
+        <v>-45.2</v>
       </c>
       <c r="E15" s="3"/>
     </row>
@@ -7130,13 +7379,13 @@
         <v>133</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="17">
-        <v>-47.6</v>
+        <v>-46.9</v>
       </c>
       <c r="E16" s="3"/>
     </row>
@@ -7144,14 +7393,14 @@
       <c r="A17" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>205</v>
+      <c r="B17" s="25" t="s">
+        <v>235</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="17">
-        <v>-42.1</v>
+        <v>-45.7</v>
       </c>
       <c r="E17" s="3"/>
     </row>
@@ -7159,14 +7408,14 @@
       <c r="A18" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>202</v>
+      <c r="B18" s="40" t="s">
+        <v>257</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="17">
-        <v>-44.4</v>
+        <v>-44.7</v>
       </c>
       <c r="E18" s="2"/>
     </row>
@@ -7174,14 +7423,14 @@
       <c r="A19" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>214</v>
+      <c r="B19" s="40" t="s">
+        <v>259</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="17">
-        <v>-43.9</v>
+        <v>-46.5</v>
       </c>
       <c r="E19" s="3"/>
     </row>
@@ -7189,14 +7438,14 @@
       <c r="A20" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>215</v>
+      <c r="B20" s="25" t="s">
+        <v>242</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="17">
-        <v>-43.6</v>
+        <v>-45.7</v>
       </c>
       <c r="E20" s="3"/>
     </row>
@@ -7205,13 +7454,13 @@
         <v>138</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>-44.1</v>
+        <v>-44.9</v>
       </c>
       <c r="E21" s="3"/>
     </row>
@@ -7219,14 +7468,14 @@
       <c r="A22" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="39" t="s">
-        <v>216</v>
+      <c r="B22" s="25" t="s">
+        <v>262</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="17">
-        <v>-45.9</v>
+        <v>-48.5</v>
       </c>
       <c r="E22" s="3"/>
     </row>
@@ -7235,13 +7484,13 @@
         <v>140</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="17">
-        <v>-42.8</v>
+        <v>-44.5</v>
       </c>
       <c r="E23" s="3"/>
     </row>
@@ -7249,14 +7498,14 @@
       <c r="A24" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>214</v>
+      <c r="B24" s="40" t="s">
+        <v>241</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="17">
-        <v>-45.5</v>
+        <v>-49.6</v>
       </c>
       <c r="E24" s="3"/>
     </row>
@@ -7265,13 +7514,13 @@
         <v>142</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="17">
-        <v>-45.5</v>
+        <v>-49.2</v>
       </c>
       <c r="E25" s="3"/>
     </row>
@@ -7279,14 +7528,14 @@
       <c r="A26" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>206</v>
+      <c r="B26" s="40" t="s">
+        <v>258</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="17">
-        <v>-42.5</v>
+        <v>-45.3</v>
       </c>
       <c r="E26" s="3"/>
     </row>
@@ -7294,14 +7543,14 @@
       <c r="A27" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>219</v>
+      <c r="B27" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="17">
-        <v>-43.7</v>
+        <v>-47.4</v>
       </c>
       <c r="E27" s="3"/>
     </row>
@@ -7309,14 +7558,14 @@
       <c r="A28" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>220</v>
+      <c r="B28" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="17">
-        <v>-43.3</v>
+        <v>-44.7</v>
       </c>
       <c r="E28" s="2"/>
     </row>
@@ -7324,14 +7573,14 @@
       <c r="A29" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>220</v>
+      <c r="B29" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D29" s="17">
-        <v>-44.7</v>
+        <v>-46.3</v>
       </c>
       <c r="E29" s="3"/>
     </row>
@@ -7339,14 +7588,14 @@
       <c r="A30" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>201</v>
+      <c r="B30" s="40" t="s">
+        <v>260</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="17">
-        <v>-44.5</v>
+        <v>-46</v>
       </c>
       <c r="E30" s="3"/>
     </row>
@@ -7355,13 +7604,13 @@
         <v>148</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="17">
-        <v>-41.5</v>
+        <v>-41.9</v>
       </c>
       <c r="E31" s="3"/>
     </row>
@@ -7370,13 +7619,13 @@
         <v>149</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="17">
-        <v>-45.3</v>
+        <v>-46.1</v>
       </c>
       <c r="E32" s="3"/>
     </row>
@@ -7384,14 +7633,14 @@
       <c r="A33" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>222</v>
+      <c r="B33" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="17">
-        <v>-43.7</v>
+        <v>-46.1</v>
       </c>
       <c r="E33" s="3"/>
     </row>
@@ -7399,14 +7648,14 @@
       <c r="A34" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>196</v>
+      <c r="B34" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="17">
-        <v>-39.799999999999997</v>
+        <v>-41.3</v>
       </c>
       <c r="E34" s="3"/>
     </row>
@@ -7415,13 +7664,13 @@
         <v>152</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="17">
-        <v>-45</v>
+        <v>-45.8</v>
       </c>
       <c r="E35" s="3"/>
     </row>
@@ -7429,14 +7678,14 @@
       <c r="A36" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>196</v>
+      <c r="B36" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="16">
-        <v>-39.200000000000003</v>
+      <c r="D36" s="17">
+        <v>-42.7</v>
       </c>
       <c r="E36" s="3"/>
     </row>
@@ -7445,13 +7694,13 @@
         <v>154</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="17">
-        <v>-41.1</v>
+        <v>-44.3</v>
       </c>
       <c r="E37" s="3"/>
     </row>
@@ -7459,14 +7708,14 @@
       <c r="A38" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>223</v>
+      <c r="B38" s="43" t="s">
+        <v>195</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="17">
-        <v>-41</v>
+      <c r="D38" s="16">
+        <v>-39.700000000000003</v>
       </c>
       <c r="E38" s="3"/>
     </row>
@@ -7474,14 +7723,14 @@
       <c r="A39" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>224</v>
+      <c r="B39" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="17">
-        <v>-42.3</v>
+        <v>-48.1</v>
       </c>
       <c r="E39" s="3"/>
     </row>
@@ -7489,323 +7738,56 @@
       <c r="A40" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>196</v>
+      <c r="B40" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="17">
-        <v>-39.4</v>
+        <v>-42.4</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>222</v>
+        <v>266</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="17">
-        <v>-41.4</v>
+        <v>-45.5</v>
       </c>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="17">
-        <v>-44.3</v>
-      </c>
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="17">
-        <v>-43.6</v>
-      </c>
-      <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="17">
-        <v>-40.700000000000003</v>
-      </c>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="17">
-        <v>-43.4</v>
-      </c>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="17">
-        <v>-47.5</v>
-      </c>
-      <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="17">
-        <v>-40.299999999999997</v>
-      </c>
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="17">
-        <v>-42</v>
-      </c>
-      <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="17">
-        <v>-41</v>
-      </c>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="17">
-        <v>-41.5</v>
-      </c>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="17">
-        <v>-42.6</v>
-      </c>
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="16">
-        <v>-39.200000000000003</v>
-      </c>
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="17">
-        <v>-42</v>
-      </c>
-      <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="17">
-        <v>-40.4</v>
-      </c>
-      <c r="E54" s="3"/>
-    </row>
-    <row r="55" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="17">
-        <v>-44.7</v>
-      </c>
-      <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="17">
-        <v>-43.8</v>
-      </c>
-      <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="17">
-        <v>-44.2</v>
-      </c>
-      <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B58" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="17">
-        <v>-43.2</v>
-      </c>
-      <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="17">
-        <v>-42.1</v>
-      </c>
-      <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:5" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C60" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="D60" s="47"/>
+    <row r="42" spans="1:5" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="D42" s="49"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D41">
+    <sortCondition ref="A3:A41"/>
+  </sortState>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C42:D42"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D3:D59">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="D3:D41">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7815,7 +7797,7 @@
         <color rgb="FF3A0CA3"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
